--- a/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Basic_Tech.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Basic_Tech.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D41D8-DD34-4550-9E3C-885E22FA941C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA7885-FE8A-41FE-87B9-51CFEC96E6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,6 +93,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -120,9 +136,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,13 +516,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>77</v>
@@ -518,13 +536,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>76</v>
@@ -541,32 +559,32 @@
         <v>33</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>33</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3">
         <v>28</v>
       </c>
       <c r="E5" s="1">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
         <v>76</v>
       </c>
     </row>
@@ -578,13 +596,13 @@
         <v>15</v>
       </c>
       <c r="C6" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>76</v>
@@ -598,13 +616,13 @@
         <v>15</v>
       </c>
       <c r="C7" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>76</v>
@@ -621,10 +639,10 @@
         <v>34</v>
       </c>
       <c r="D8" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
         <v>77</v>
@@ -644,7 +662,7 @@
         <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
         <v>72</v>
